--- a/_Drive/Publicacoes/vernilli.xlsx
+++ b/_Drive/Publicacoes/vernilli.xlsx
@@ -4,7 +4,7 @@
   <fileVersion lastEdited="4" lowestEdited="4" rupBuild="3820"/>
   <workbookPr date1904="0"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView activeTab="0" windowWidth="14400" windowHeight="6300"/>
   </bookViews>
   <sheets>
     <sheet name="vernilli.doi" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,29 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1" count="1">
+  <si>
+    <t>DOI</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
+      <i val="0"/>
+      <u val="none"/>
+      <color rgb="FF000000"/>
+      <name val="Sans"/>
+      <vertAlign val="baseline"/>
+      <sz val="10"/>
+      <strike val="0"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="0"/>
       <u val="none"/>
       <color rgb="FF000000"/>
@@ -62,8 +80,12 @@
       <protection locked="1" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -76,189 +98,195 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="256" style="0" width="9.142307692307693"/>
+    <col min="1" max="1" style="0" width="37.569170673076925" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" style="0" width="9.142307692307693"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>10.1590/1980-5373-mr-2016-0875</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.869.1007</t>
+          <t>10.1590/1980-5373-mr-2016-0875</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.798-799.487</t>
+          <t>10.4028/www.scientific.net/msf.869.1007</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.1016/j.resconrec.2017.08.021</t>
+          <t>10.4028/www.scientific.net/msf.798-799.487</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2006.04.040</t>
+          <t>10.1016/j.resconrec.2017.08.021</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.1179/174328108x287784</t>
+          <t>10.1016/j.msea.2006.04.040</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.1016/j.ceramint.2004.09.016</t>
+          <t>10.1179/174328108x287784</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.805.331</t>
+          <t>10.1016/j.ceramint.2004.09.016</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.775-776.642</t>
+          <t>10.4028/www.scientific.net/msf.805.331</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.1016/j.applthermaleng.2012.10.004</t>
+          <t>10.4028/www.scientific.net/msf.775-776.642</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.1016/j.jmrt.2019.09.038</t>
+          <t>10.1016/j.applthermaleng.2012.10.004</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.1590/s0366-69132001000300005</t>
+          <t>10.1016/j.jmrt.2019.09.038</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.1590/s0366-69132001000300004</t>
+          <t>10.1590/s0366-69132001000300005</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1016/j.jclepro.2017.10.130</t>
+          <t>10.1590/s0366-69132001000300004</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10.1080/03019233.2016.1155007</t>
+          <t>10.1016/j.jclepro.2017.10.130</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1179/174328105x48160</t>
+          <t>10.1080/03019233.2016.1155007</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1016/j.matchar.2006.01.022</t>
+          <t>10.1179/174328105x48160</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.1590/s0366-69132000000100007</t>
+          <t>10.1016/j.matchar.2006.01.022</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.1590/S0366-69132001000300003</t>
+          <t>10.1590/s0366-69132000000100007</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.1590/s1517-70762007000200004</t>
+          <t>10.1590/S0366-69132001000300003</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.1590/S0366-69131999000200006</t>
+          <t>10.1590/s1517-70762007000200004</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.1016/j.powtec.2019.08.003</t>
+          <t>10.1590/S0366-69131999000200006</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.775-776.607</t>
+          <t>10.1016/j.powtec.2019.08.003</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.798-799.526</t>
+          <t>10.4028/www.scientific.net/msf.775-776.607</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.1002/srin.201200085</t>
+          <t>10.4028/www.scientific.net/msf.798-799.526</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="inlineStr">
+        <is>
+          <t>10.1002/srin.201200085</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>10.1002/maco.201106390</t>
         </is>
